--- a/employeedata.xlsx
+++ b/employeedata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/jayalakshmi_anand_uipath_com/Documents/Documents/UiPath/My Projects/Certification practice/certificatepractice/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uipath-my.sharepoint.com/personal/jayalakshmi_anand_uipath_com/Documents/Documents/UiPath/My Projects/Certification practice/certificatepractice_Windows/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="44" documentId="11_F25DC773A252ABDACC1048F5891A617E5ADE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{814DFEBE-D05B-49C1-9D79-1F3FC589771D}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="120" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -129,10 +129,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
